--- a/data_lake/industry/CFM/eMMC.xlsx
+++ b/data_lake/industry/CFM/eMMC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14932FC8-A8D2-418D-8595-72BE11A02C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480C701A-F0E5-0A49-A876-C797061F9D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18060" yWindow="780" windowWidth="17940" windowHeight="20760" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="eMMC 8GB 5.1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -72,29 +72,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -132,42 +132,42 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -445,19 +445,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -503,7 +503,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -526,7 +526,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -549,7 +549,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -572,7 +572,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -595,7 +595,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -618,7 +618,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -641,7 +641,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -664,7 +664,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -687,7 +687,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -710,7 +710,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -733,7 +733,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -756,7 +756,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -779,7 +779,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -802,7 +802,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -825,7 +825,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -848,7 +848,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -871,7 +871,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -894,7 +894,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -917,7 +917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -940,7 +940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -963,7 +963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -1673,6 +1673,167 @@
         <v>20.5</v>
       </c>
       <c r="G53" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F54" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G54" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F55" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G55" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F56" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G56" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F57" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G57" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F58" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G58" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F59" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G59" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F60" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="G60" s="9">
         <v>20</v>
       </c>
     </row>
@@ -1684,19 +1845,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3458BA-C690-425E-897C-D26F43A0AC55}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1719,7 +1880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1742,7 +1903,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1765,7 +1926,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1788,7 +1949,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1811,7 +1972,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1834,7 +1995,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1857,7 +2018,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1880,7 +2041,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1903,7 +2064,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1926,7 +2087,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1949,7 +2110,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1972,7 +2133,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1995,7 +2156,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2018,7 +2179,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2041,7 +2202,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2064,7 +2225,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2087,7 +2248,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2110,7 +2271,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2133,7 +2294,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2156,7 +2317,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2179,7 +2340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2202,7 +2363,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2225,7 +2386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2248,7 +2409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2271,7 +2432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2294,7 +2455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2317,7 +2478,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2340,7 +2501,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2363,7 +2524,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2386,7 +2547,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2409,7 +2570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2432,7 +2593,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2455,7 +2616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2478,7 +2639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2501,7 +2662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2524,7 +2685,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2547,7 +2708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2570,7 +2731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2593,7 +2754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2616,7 +2777,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2639,7 +2800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2662,7 +2823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2685,7 +2846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2708,7 +2869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2731,7 +2892,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2754,7 +2915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2777,7 +2938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2800,7 +2961,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -2823,7 +2984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -2846,7 +3007,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -2869,7 +3030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -2892,7 +3053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -2912,6 +3073,167 @@
         <v>22.3</v>
       </c>
       <c r="G53" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F54" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G54" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F55" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G55" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F56" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G56" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F57" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G57" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F58" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G58" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F59" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G59" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>20.8</v>
+      </c>
+      <c r="F60" s="9">
+        <v>22.3</v>
+      </c>
+      <c r="G60" s="9">
         <v>21</v>
       </c>
     </row>
@@ -2923,19 +3245,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4C3C62-4D14-4156-9017-943BF365E5C9}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2958,7 +3280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2981,7 +3303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3004,7 +3326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3027,7 +3349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3050,7 +3372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3073,7 +3395,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3096,7 +3418,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3119,7 +3441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3142,7 +3464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3165,7 +3487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3188,7 +3510,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3211,7 +3533,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3234,7 +3556,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3257,7 +3579,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3280,7 +3602,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3303,7 +3625,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3326,7 +3648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3349,7 +3671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3372,7 +3694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3395,7 +3717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3418,7 +3740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3441,7 +3763,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3464,7 +3786,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3487,7 +3809,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3510,7 +3832,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3533,7 +3855,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3556,7 +3878,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3579,7 +3901,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3602,7 +3924,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3625,7 +3947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3648,7 +3970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3671,7 +3993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3694,7 +4016,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3717,7 +4039,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3740,7 +4062,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3763,7 +4085,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3786,7 +4108,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3809,7 +4131,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3832,7 +4154,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3855,7 +4177,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3878,7 +4200,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3901,7 +4223,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3924,7 +4246,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3947,7 +4269,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3970,7 +4292,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3993,7 +4315,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4016,7 +4338,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4039,7 +4361,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -4062,7 +4384,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -4085,7 +4407,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -4108,7 +4430,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -4131,7 +4453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -4152,6 +4474,167 @@
       </c>
       <c r="G53" s="9">
         <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>22.6</v>
+      </c>
+      <c r="F54" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="G54" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>22.6</v>
+      </c>
+      <c r="F55" s="9">
+        <v>24.3</v>
+      </c>
+      <c r="G55" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>21.6</v>
+      </c>
+      <c r="F56" s="9">
+        <v>23.3</v>
+      </c>
+      <c r="G56" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>21.6</v>
+      </c>
+      <c r="F57" s="9">
+        <v>23.3</v>
+      </c>
+      <c r="G57" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>21.6</v>
+      </c>
+      <c r="F58" s="9">
+        <v>23.3</v>
+      </c>
+      <c r="G58" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>21.6</v>
+      </c>
+      <c r="F59" s="9">
+        <v>23.3</v>
+      </c>
+      <c r="G59" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>21.6</v>
+      </c>
+      <c r="F60" s="9">
+        <v>23.3</v>
+      </c>
+      <c r="G60" s="9">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4162,19 +4645,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB386A95-5195-4084-9FB9-971921256B62}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4197,7 +4680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4220,7 +4703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4243,7 +4726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4266,7 +4749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4289,7 +4772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4312,7 +4795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4335,7 +4818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4358,7 +4841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4381,7 +4864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4404,7 +4887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4427,7 +4910,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4450,7 +4933,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4473,7 +4956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4496,7 +4979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4519,7 +5002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4542,7 +5025,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4565,7 +5048,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4588,7 +5071,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4611,7 +5094,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4634,7 +5117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4657,7 +5140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4680,7 +5163,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4703,7 +5186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4726,7 +5209,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4749,7 +5232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4772,7 +5255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4795,7 +5278,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4818,7 +5301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4841,7 +5324,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4864,7 +5347,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4887,7 +5370,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4910,7 +5393,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4933,7 +5416,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4956,7 +5439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4979,7 +5462,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5002,7 +5485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5025,7 +5508,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5048,7 +5531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5071,7 +5554,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5094,7 +5577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5117,7 +5600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5140,7 +5623,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5163,7 +5646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5186,7 +5669,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -5209,7 +5692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -5232,7 +5715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -5255,7 +5738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -5278,7 +5761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -5301,7 +5784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -5324,7 +5807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -5347,7 +5830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -5370,7 +5853,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -5391,6 +5874,167 @@
       </c>
       <c r="G53" s="9">
         <v>23.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>23</v>
+      </c>
+      <c r="F54" s="9">
+        <v>24.5</v>
+      </c>
+      <c r="G54" s="9">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>23</v>
+      </c>
+      <c r="F55" s="9">
+        <v>24.5</v>
+      </c>
+      <c r="G55" s="9">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>22</v>
+      </c>
+      <c r="F56" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="G56" s="9">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>22</v>
+      </c>
+      <c r="F57" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="G57" s="9">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>22</v>
+      </c>
+      <c r="F58" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="G58" s="9">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>22</v>
+      </c>
+      <c r="F59" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="G59" s="9">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>22</v>
+      </c>
+      <c r="F60" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="G60" s="9">
+        <v>22.5</v>
       </c>
     </row>
   </sheetData>
@@ -5401,19 +6045,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29CFE0E-1939-4F13-BC18-8B4E3159446B}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5436,7 +6080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5459,7 +6103,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5482,7 +6126,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5505,7 +6149,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5528,7 +6172,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5551,7 +6195,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5574,7 +6218,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5597,7 +6241,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5620,7 +6264,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5643,7 +6287,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5666,7 +6310,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5689,7 +6333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5712,7 +6356,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5735,7 +6379,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5758,7 +6402,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5781,7 +6425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5804,7 +6448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5827,7 +6471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5850,7 +6494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5873,7 +6517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5896,7 +6540,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5919,7 +6563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5942,7 +6586,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5965,7 +6609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -5988,7 +6632,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6011,7 +6655,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6034,7 +6678,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6057,7 +6701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6080,7 +6724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6103,7 +6747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6126,7 +6770,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6149,7 +6793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6172,7 +6816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6195,7 +6839,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6218,7 +6862,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6241,7 +6885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6264,7 +6908,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6287,7 +6931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6310,7 +6954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -6333,7 +6977,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -6356,7 +7000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -6379,7 +7023,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -6402,7 +7046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -6425,7 +7069,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -6448,7 +7092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -6471,7 +7115,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -6494,7 +7138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -6517,7 +7161,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -6540,7 +7184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -6563,7 +7207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -6586,7 +7230,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -6609,7 +7253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -6629,6 +7273,167 @@
         <v>33.5</v>
       </c>
       <c r="G53" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F54" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G54" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F55" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G55" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F56" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G56" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F57" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G57" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F58" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G58" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F59" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G59" s="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="F60" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="G60" s="9">
         <v>31</v>
       </c>
     </row>
@@ -6640,19 +7445,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEFF7D63-8706-4CE6-8EDE-86A6F3873A2B}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6675,7 +7480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6698,7 +7503,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6721,7 +7526,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6744,7 +7549,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6767,7 +7572,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6790,7 +7595,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6813,7 +7618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6836,7 +7641,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6859,7 +7664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6882,7 +7687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6905,7 +7710,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6928,7 +7733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6951,7 +7756,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6974,7 +7779,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -6997,7 +7802,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7020,7 +7825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7043,7 +7848,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7066,7 +7871,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7089,7 +7894,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7112,7 +7917,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7135,7 +7940,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7158,7 +7963,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7181,7 +7986,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7204,7 +8009,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7227,7 +8032,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -7250,7 +8055,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -7273,7 +8078,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -7296,7 +8101,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -7319,7 +8124,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -7342,7 +8147,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -7365,7 +8170,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -7388,7 +8193,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -7411,7 +8216,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -7434,7 +8239,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -7457,7 +8262,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -7480,7 +8285,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -7503,7 +8308,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -7526,7 +8331,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -7549,7 +8354,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -7572,7 +8377,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -7595,7 +8400,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -7618,7 +8423,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -7641,7 +8446,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -7664,7 +8469,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -7687,7 +8492,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -7710,7 +8515,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -7733,7 +8538,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -7756,7 +8561,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -7779,7 +8584,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -7802,7 +8607,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -7825,7 +8630,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -7848,7 +8653,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -7868,6 +8673,167 @@
         <v>60.5</v>
       </c>
       <c r="G53" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F54" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G54" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F55" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G55" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F56" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G56" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F57" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G57" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F58" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G58" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F59" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G59" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F60" s="9">
+        <v>60.5</v>
+      </c>
+      <c r="G60" s="9">
         <v>58</v>
       </c>
     </row>
